--- a/data/trans_orig/P36BPD06_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD06_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de mantequilla, margarina o nata que consume al día en 2023</t>
+          <t>Población según el número de raciones de mantequilla, margarina o nata que consume al día en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79134</t>
+          <t>78876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115286</t>
+          <t>114269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77874</t>
+          <t>77558</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106743</t>
+          <t>106770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160912</t>
+          <t>163301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211300</t>
+          <t>211138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>388677</t>
+          <t>389694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424829</t>
+          <t>425087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340724</t>
+          <t>340697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>369593</t>
+          <t>369909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740130</t>
+          <t>740292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>790518</t>
+          <t>788129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86733</t>
+          <t>86121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121364</t>
+          <t>121023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66290</t>
+          <t>66346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93001</t>
+          <t>93219</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159970</t>
+          <t>158679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>204271</t>
+          <t>204296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329487</t>
+          <t>329828</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364118</t>
+          <t>364730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288951</t>
+          <t>288733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>315662</t>
+          <t>315606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>628532</t>
+          <t>628507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>672833</t>
+          <t>674124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31307</t>
+          <t>33007</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155285</t>
+          <t>155756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29819</t>
+          <t>29761</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46864</t>
+          <t>46103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52866</t>
+          <t>62813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192157</t>
+          <t>191759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508813</t>
+          <t>508342</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632791</t>
+          <t>631091</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119885</t>
+          <t>120646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136930</t>
+          <t>136988</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638690</t>
+          <t>639088</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>777981</t>
+          <t>768034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217118</t>
+          <t>220471</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>287786</t>
+          <t>288314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>188168</t>
+          <t>185800</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>642527</t>
+          <t>677970</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>439286</t>
+          <t>434004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1017216</t>
+          <t>1011694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>744487</t>
+          <t>743959</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>815155</t>
+          <t>811802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>333940</t>
+          <t>298497</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>788299</t>
+          <t>790667</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>991524</t>
+          <t>997046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1569454</t>
+          <t>1574736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107713</t>
+          <t>108427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147325</t>
+          <t>149196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>204105</t>
+          <t>203497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>426520</t>
+          <t>408250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>330991</t>
+          <t>332007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>558123</t>
+          <t>556804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324184</t>
+          <t>322313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>363796</t>
+          <t>363082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>413082</t>
+          <t>431352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>635497</t>
+          <t>636105</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>752988</t>
+          <t>754307</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>980120</t>
+          <t>979104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32769</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71299</t>
+          <t>70404</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>196550</t>
+          <t>197305</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243045</t>
+          <t>240977</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>239304</t>
+          <t>241207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>303334</t>
+          <t>302837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169208</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207738</t>
+          <t>208600</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>517764</t>
+          <t>519832</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>564259</t>
+          <t>563504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,17 +2623,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>731695</t>
+          <t>731696</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>697982</t>
+          <t>698480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>762012</t>
+          <t>760110</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001316</t>
+          <t>1001317</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001316</t>
+          <t>1001317</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001316</t>
+          <t>1001317</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>548752</t>
+          <t>530769</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>790354</t>
+          <t>794030</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>856680</t>
+          <t>849031</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1542152</t>
+          <t>1543542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1539335</t>
+          <t>1533663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2324433</t>
+          <t>2292439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2572847</t>
+          <t>2569171</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2814449</t>
+          <t>2832432</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2030895</t>
+          <t>2029505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2716367</t>
+          <t>2724016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4611814</t>
+          <t>4643808</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5396912</t>
+          <t>5402584</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD06_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD06_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94817</t>
+          <t>107487</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78876</t>
+          <t>89188</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114269</t>
+          <t>129222</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>91126</t>
+          <t>102358</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77558</t>
+          <t>88380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106770</t>
+          <t>120372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>185943</t>
+          <t>209845</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163301</t>
+          <t>186880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211138</t>
+          <t>236375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>409146</t>
+          <t>441876</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>389694</t>
+          <t>420141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425087</t>
+          <t>460175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>356341</t>
+          <t>386053</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340697</t>
+          <t>368039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>369909</t>
+          <t>400031</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>765487</t>
+          <t>827928</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740292</t>
+          <t>801398</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>788129</t>
+          <t>850893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503963</t>
+          <t>549363</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503963</t>
+          <t>549363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503963</t>
+          <t>549363</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951430</t>
+          <t>1037773</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951430</t>
+          <t>1037773</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951430</t>
+          <t>1037773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>103211</t>
+          <t>114027</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86121</t>
+          <t>96801</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121023</t>
+          <t>133643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79363</t>
+          <t>91937</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66346</t>
+          <t>77277</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93219</t>
+          <t>108000</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>182574</t>
+          <t>205964</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158679</t>
+          <t>181481</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>204296</t>
+          <t>228642</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>347640</t>
+          <t>367825</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329828</t>
+          <t>348209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364730</t>
+          <t>385051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>302589</t>
+          <t>330557</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288733</t>
+          <t>314494</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>315606</t>
+          <t>345217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>650229</t>
+          <t>698383</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>628507</t>
+          <t>675705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>674124</t>
+          <t>722866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>79,93%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>450851</t>
+          <t>481852</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>450851</t>
+          <t>481852</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>450851</t>
+          <t>481852</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381952</t>
+          <t>422494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381952</t>
+          <t>422494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381952</t>
+          <t>422494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832803</t>
+          <t>904347</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832803</t>
+          <t>904347</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832803</t>
+          <t>904347</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>92743</t>
+          <t>107739</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33007</t>
+          <t>92031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155756</t>
+          <t>127375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37754</t>
+          <t>43218</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46103</t>
+          <t>53076</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>130496</t>
+          <t>150957</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62813</t>
+          <t>131523</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191759</t>
+          <t>172674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>571355</t>
+          <t>359510</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508342</t>
+          <t>339874</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631091</t>
+          <t>375218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128995</t>
+          <t>143533</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120646</t>
+          <t>133675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136988</t>
+          <t>152564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>700351</t>
+          <t>503043</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639088</t>
+          <t>481326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>768034</t>
+          <t>522477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>79,89%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>664098</t>
+          <t>467249</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>664098</t>
+          <t>467249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>664098</t>
+          <t>467249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>186751</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>186751</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>186751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>830847</t>
+          <t>654000</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>830847</t>
+          <t>654000</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>830847</t>
+          <t>654000</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>252166</t>
+          <t>277662</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220471</t>
+          <t>248770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>288314</t>
+          <t>309456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>358318</t>
+          <t>179444</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185800</t>
+          <t>158260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>677970</t>
+          <t>201724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>610484</t>
+          <t>457106</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>434004</t>
+          <t>420989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1011694</t>
+          <t>497716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>780107</t>
+          <t>850679</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>743959</t>
+          <t>818885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>811802</t>
+          <t>879571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>618149</t>
+          <t>680073</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>298497</t>
+          <t>657793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>790667</t>
+          <t>701257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1398256</t>
+          <t>1530752</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>997046</t>
+          <t>1490142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1574736</t>
+          <t>1566869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,82%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1032273</t>
+          <t>1128341</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1032273</t>
+          <t>1128341</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1032273</t>
+          <t>1128341</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976467</t>
+          <t>859517</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976467</t>
+          <t>859517</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976467</t>
+          <t>859517</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2008740</t>
+          <t>1987858</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2008740</t>
+          <t>1987858</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2008740</t>
+          <t>1987858</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>127022</t>
+          <t>149677</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108427</t>
+          <t>128502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149196</t>
+          <t>176973</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>266305</t>
+          <t>227336</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203497</t>
+          <t>207838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>408250</t>
+          <t>250325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>393327</t>
+          <t>377013</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>332007</t>
+          <t>347894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>556804</t>
+          <t>412544</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>344487</t>
+          <t>414508</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322313</t>
+          <t>387212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>363082</t>
+          <t>435683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>573297</t>
+          <t>601230</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>431352</t>
+          <t>578241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>636105</t>
+          <t>620728</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>917784</t>
+          <t>1015739</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>754307</t>
+          <t>980208</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>979104</t>
+          <t>1044858</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,02%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>471509</t>
+          <t>564185</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>471509</t>
+          <t>564185</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>471509</t>
+          <t>564185</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>839602</t>
+          <t>828566</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>839602</t>
+          <t>828566</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>839602</t>
+          <t>828566</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1311111</t>
+          <t>1392752</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1311111</t>
+          <t>1392752</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1311111</t>
+          <t>1392752</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48989</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31907</t>
+          <t>45748</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70404</t>
+          <t>86690</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>220632</t>
+          <t>250260</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>197305</t>
+          <t>224313</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>240977</t>
+          <t>276923</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>269621</t>
+          <t>314304</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>241207</t>
+          <t>281352</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>302837</t>
+          <t>346629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>191518</t>
+          <t>173184</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>150538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208600</t>
+          <t>191480</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>540177</t>
+          <t>593449</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>519832</t>
+          <t>566786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>563504</t>
+          <t>619396</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>731696</t>
+          <t>766632</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>698480</t>
+          <t>734307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>760110</t>
+          <t>799584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760809</t>
+          <t>843709</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760809</t>
+          <t>843709</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760809</t>
+          <t>843709</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001317</t>
+          <t>1080936</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001317</t>
+          <t>1080936</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001317</t>
+          <t>1080936</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>718948</t>
+          <t>820636</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>530769</t>
+          <t>768719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>794030</t>
+          <t>877810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1053498</t>
+          <t>894553</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>849031</t>
+          <t>849882</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1543542</t>
+          <t>940261</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1772446</t>
+          <t>1715189</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1533663</t>
+          <t>1650217</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2292439</t>
+          <t>1789976</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2644253</t>
+          <t>2607582</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2569171</t>
+          <t>2550408</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2832432</t>
+          <t>2659499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2519549</t>
+          <t>2734895</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2029505</t>
+          <t>2689187</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2724016</t>
+          <t>2779566</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5163801</t>
+          <t>5342477</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4643808</t>
+          <t>5267690</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5402584</t>
+          <t>5407449</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3363201</t>
+          <t>3428218</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3363201</t>
+          <t>3428218</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3363201</t>
+          <t>3428218</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573047</t>
+          <t>3629448</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573047</t>
+          <t>3629448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573047</t>
+          <t>3629448</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6936247</t>
+          <t>7057666</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6936247</t>
+          <t>7057666</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6936247</t>
+          <t>7057666</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
